--- a/10.11-10.23 L&F横ぐし確認/10.16新需求1/insert_定義書対比_差異精査結果.xlsx
+++ b/10.11-10.23 L&F横ぐし確認/10.16新需求1/insert_定義書対比_差異精査結果.xlsx
@@ -313,6 +313,1425 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1098176</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3989294</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26B4C66A-E3B6-ED37-B8A6-AE1102CACDC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1098176" y="1568823"/>
+          <a:ext cx="2891118" cy="974912"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 57698"/>
+            <a:gd name="adj2" fmla="val -112005"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・資材が正しい</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・マスタ定義書が誤り</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> →要修正</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>526676</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>20017</xdr:colOff>
+      <xdr:row>260</xdr:row>
+      <xdr:rowOff>69241</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B174089C-046E-40F4-3337-F6BD29C6CB07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="526676" y="3126441"/>
+          <a:ext cx="10945753" cy="6344535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>504265</xdr:colOff>
+      <xdr:row>263</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4886377</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>69048</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{458435C1-CD40-2FD0-CF89-D634B1A8B9A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="504265" y="10040470"/>
+          <a:ext cx="4382112" cy="943107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>915876</xdr:colOff>
+      <xdr:row>282</xdr:row>
+      <xdr:rowOff>39998</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6A22FF2-30C4-41F9-5A5E-A7B37AC1EEB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11418794"/>
+          <a:ext cx="6563641" cy="1552792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>406706</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>159353</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A3D935C-E5E4-FD08-079A-CE6143F2B2CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="5468471"/>
+          <a:ext cx="7544853" cy="1638529"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>416232</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>109411</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A815CDA9-EC75-F1F1-34C6-2C9C9B4BDA56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="3944471"/>
+          <a:ext cx="7554379" cy="1095528"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>179295</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>452659</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>7509</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16497959-7C04-A33C-BEC1-B8F4594303FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="179295" y="9715500"/>
+          <a:ext cx="7602011" cy="1609950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>156882</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>430246</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>116155</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5E622B-5DF9-6B51-E3BE-B46F8EB0C4C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="156882" y="8169088"/>
+          <a:ext cx="7602011" cy="1247949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>714890</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>79453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A36CD985-3E36-59FF-1C1C-7BF6FB59A0A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11990294"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>714890</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>79453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212D8BAE-9922-D821-B283-549263F76941}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="22243676"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1647264</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123266</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 角を丸めた四角形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22677541-8F6F-4617-9C57-A569CAE626CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1647264" y="1905002"/>
+          <a:ext cx="7463117" cy="1804146"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -40500"/>
+            <a:gd name="adj2" fmla="val -78465"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・資材が誤り</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> →要修正。正しくは以下の認識</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>UPDATE MST_CODE_TBL SET DSP_ORDER = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>104</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> WHERE CODE_CNF_ID = 34 AND DSP_ORDER = 103;</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>UPDATE MST_CODE_TBL SET DSP_ORDER = 103 WHERE CODE_CNF_ID = 33 AND DSP_ORDER = 102;</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>INSERT INTO MST_CODE_TBL VALUES(67 , '</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プルダウンコメント</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>' , '002' , '21' , '</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>該当あり（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>情報）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>' , </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>102</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> , 'N');</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>INSERT INTO MST_CODE_TBL VALUES(68 , '</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プルダウンコメント</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>' , '002' , '22' , '</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>取消し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>' , </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>105</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> , 'N');</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・マスタ定義書が正しい</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>907676</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>78440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134471</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="吹き出し: 角を丸めた四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2A76009-CF4E-400E-AF41-6B4186A30F26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8236323" y="4504764"/>
+          <a:ext cx="907677" cy="717177"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78837"/>
+            <a:gd name="adj2" fmla="val -27630"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>918883</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>145678</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>156883</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="吹き出し: 角を丸めた四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2ABE480-41B3-4964-B632-826D63608C16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8247530" y="6219265"/>
+          <a:ext cx="907677" cy="717177"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78837"/>
+            <a:gd name="adj2" fmla="val -27630"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>179295</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="吹き出し: 角を丸めた四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97899760-0471-49C4-B478-75A0FA25B8EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8281147" y="8561294"/>
+          <a:ext cx="907677" cy="717177"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78837"/>
+            <a:gd name="adj2" fmla="val -27630"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>869577</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>40340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>96372</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>85164</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="吹き出し: 角を丸めた四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F73C17C3-A9E9-461B-9A6C-5B055478A03C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8198224" y="10349752"/>
+          <a:ext cx="907677" cy="717177"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78837"/>
+            <a:gd name="adj2" fmla="val -27630"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1221440</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>448235</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="吹き出し: 角を丸めた四角形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A580AE85-03D9-48DC-B206-8847C07EE6A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6869205" y="14713323"/>
+          <a:ext cx="907677" cy="717177"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78837"/>
+            <a:gd name="adj2" fmla="val -27630"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>896471</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>549088</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="吹き出し: 角を丸めた四角形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2B42556-04FD-442D-B199-3281E0FFC72B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14948647" y="24720176"/>
+          <a:ext cx="3171265" cy="1344706"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -68236"/>
+            <a:gd name="adj2" fmla="val -15130"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>NG</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>「該当あり（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>情報）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>と、「該当あり（その他）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>の表示順がヒアリングシートと逆転している</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>930088</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>739588</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="吹き出し: 角を丸めた四角形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E989267-18B5-4EA4-8309-BC60333C1562}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9939617" y="1479176"/>
+          <a:ext cx="3171265" cy="1344706"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -72476"/>
+            <a:gd name="adj2" fmla="val -56797"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>NG</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>「該当あり（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>情報）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>と、「該当あり（その他）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>の表示順がヒアリングシートと逆転している</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -597,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -859,11 +2278,12 @@
     <mergeCell ref="F1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rIdDrw1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1486,6 +2906,7 @@
     <mergeCell ref="K1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rIdDrw1"/>
 </worksheet>
 </file>
 
